--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/INDIANA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/INDIANA_2017.xlsx
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C266">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C649">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C728">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C729">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C765">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C766">
